--- a/dados/excel/genero_gap_salarial.xlsx
+++ b/dados/excel/genero_gap_salarial.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Metadados" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Dados" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadados" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dados" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Dados'!$A$1:$I$43</definedName>
@@ -634,7 +634,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>10/10/2026 14:55</t>
+          <t>12/10/2026 16:30</t>
         </is>
       </c>
     </row>

--- a/dados/excel/genero_gap_salarial.xlsx
+++ b/dados/excel/genero_gap_salarial.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dados" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Dados'!$A$1:$I$43</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Dados'!$A$1:$I$42</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -589,7 +589,7 @@
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="10">
@@ -634,7 +634,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>12/10/2026 16:30</t>
+          <t>16/10/2026 19:58</t>
         </is>
       </c>
     </row>
@@ -830,7 +830,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I43"/>
+  <dimension ref="A1:I42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -898,75 +898,75 @@
         </is>
       </c>
       <c r="B2" s="9" t="n">
-        <v>18156.35356741573</v>
+        <v>18127.52938385269</v>
       </c>
       <c r="C2" s="10" t="n">
-        <v>21927.08078947368</v>
+        <v>21487.59010204082</v>
       </c>
       <c r="D2" s="9" t="n">
-        <v>23881.19489361702</v>
+        <v>23917.75802267003</v>
       </c>
       <c r="E2" s="9" t="n">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F2" s="11" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G2" s="9" t="n">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="H2" s="11" t="n">
-        <v>5724.84</v>
+        <v>5790.23</v>
       </c>
       <c r="I2" s="9" t="n">
-        <v>23.97</v>
+        <v>24.21</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="12" t="inlineStr">
         <is>
-          <t>AUX. DE FISCALIZACAO</t>
+          <t>FISCAL PUBLICO</t>
         </is>
       </c>
       <c r="B3" s="13" t="n">
-        <v>8103.940909090909</v>
+        <v>6331.037777777778</v>
       </c>
       <c r="C3" s="14" t="n">
-        <v>0</v>
+        <v>4119.37</v>
       </c>
       <c r="D3" s="13" t="n">
-        <v>10482.53320987654</v>
+        <v>8130.915377906977</v>
       </c>
       <c r="E3" s="13" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F3" s="15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G3" s="13" t="n">
-        <v>17</v>
+        <v>38</v>
       </c>
       <c r="H3" s="15" t="n">
-        <v>2378.59</v>
+        <v>1799.88</v>
       </c>
       <c r="I3" s="13" t="n">
-        <v>22.69</v>
+        <v>22.14</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="8" t="inlineStr">
         <is>
-          <t>FISCAL PUBLICO</t>
+          <t>AUX. DE FISCALIZACAO</t>
         </is>
       </c>
       <c r="B4" s="9" t="n">
-        <v>6331.037777777778</v>
+        <v>8295.3171</v>
       </c>
       <c r="C4" s="10" t="n">
-        <v>4119.37</v>
+        <v>6190.179</v>
       </c>
       <c r="D4" s="9" t="n">
-        <v>8130.915377906977</v>
+        <v>10482.53320987654</v>
       </c>
       <c r="E4" s="9" t="n">
         <v>10</v>
@@ -975,13 +975,13 @@
         <v>1</v>
       </c>
       <c r="G4" s="9" t="n">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="H4" s="11" t="n">
-        <v>1799.88</v>
+        <v>2187.22</v>
       </c>
       <c r="I4" s="9" t="n">
-        <v>22.14</v>
+        <v>20.87</v>
       </c>
     </row>
     <row r="5">
@@ -1049,94 +1049,94 @@
     <row r="7">
       <c r="A7" s="12" t="inlineStr">
         <is>
-          <t>CIRURGIAO DENTISTA 75H</t>
+          <t>COORDENADOR ADMINISTRATIVO(FG)</t>
         </is>
       </c>
       <c r="B7" s="13" t="n">
-        <v>17319.57536585366</v>
+        <v>15014.0926</v>
       </c>
       <c r="C7" s="14" t="n">
-        <v>22533.06272727273</v>
+        <v>19092.27769230769</v>
       </c>
       <c r="D7" s="13" t="n">
-        <v>20573.55902272727</v>
+        <v>17995.86325842697</v>
       </c>
       <c r="E7" s="13" t="n">
-        <v>41</v>
+        <v>22</v>
       </c>
       <c r="F7" s="15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G7" s="13" t="n">
-        <v>42</v>
+        <v>12</v>
       </c>
       <c r="H7" s="15" t="n">
-        <v>3253.98</v>
+        <v>2981.77</v>
       </c>
       <c r="I7" s="13" t="n">
-        <v>15.82</v>
+        <v>16.57</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="8" t="inlineStr">
         <is>
-          <t>AGENTE DE VIG.SANITARIA I</t>
+          <t>CIRURGIAO DENTISTA 75H</t>
         </is>
       </c>
       <c r="B8" s="9" t="n">
-        <v>6461.886701570681</v>
+        <v>17319.57536585366</v>
       </c>
       <c r="C8" s="10" t="n">
-        <v>6348.397</v>
+        <v>22533.06272727273</v>
       </c>
       <c r="D8" s="9" t="n">
-        <v>7588.658556149732</v>
+        <v>20573.55902272727</v>
       </c>
       <c r="E8" s="9" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="F8" s="11" t="n">
         <v>1</v>
       </c>
       <c r="G8" s="9" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="H8" s="11" t="n">
-        <v>1126.77</v>
+        <v>3253.98</v>
       </c>
       <c r="I8" s="9" t="n">
-        <v>14.85</v>
+        <v>15.82</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="12" t="inlineStr">
         <is>
-          <t>COORDENADOR ADMINISTRATIVO(FG)</t>
+          <t>AGENTE DE VIG.SANITARIA I</t>
         </is>
       </c>
       <c r="B9" s="13" t="n">
-        <v>15444.267</v>
+        <v>6461.886701570681</v>
       </c>
       <c r="C9" s="14" t="n">
-        <v>9743.593333333332</v>
+        <v>6348.397</v>
       </c>
       <c r="D9" s="13" t="n">
-        <v>17995.86325842697</v>
+        <v>7588.658556149732</v>
       </c>
       <c r="E9" s="13" t="n">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="F9" s="15" t="n">
         <v>1</v>
       </c>
       <c r="G9" s="13" t="n">
-        <v>12</v>
+        <v>39</v>
       </c>
       <c r="H9" s="15" t="n">
-        <v>2551.6</v>
+        <v>1126.77</v>
       </c>
       <c r="I9" s="13" t="n">
-        <v>14.18</v>
+        <v>14.85</v>
       </c>
     </row>
     <row r="10">
@@ -1146,90 +1146,90 @@
         </is>
       </c>
       <c r="B10" s="9" t="n">
-        <v>6982.888615702479</v>
+        <v>6985.865894736842</v>
       </c>
       <c r="C10" s="10" t="n">
-        <v>7745.81157894737</v>
+        <v>7450.078928571428</v>
       </c>
       <c r="D10" s="9" t="n">
         <v>8002.224890210429</v>
       </c>
       <c r="E10" s="9" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F10" s="11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G10" s="9" t="n">
         <v>294</v>
       </c>
       <c r="H10" s="11" t="n">
-        <v>1019.34</v>
+        <v>1016.36</v>
       </c>
       <c r="I10" s="9" t="n">
-        <v>12.74</v>
+        <v>12.7</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="12" t="inlineStr">
         <is>
-          <t>AUX. DE ADMINISTRACAO</t>
+          <t>ENFERMEIRO</t>
         </is>
       </c>
       <c r="B11" s="13" t="n">
-        <v>5382.467752655953</v>
+        <v>14737.6216903172</v>
       </c>
       <c r="C11" s="14" t="n">
-        <v>7016.67409090909</v>
+        <v>16139.0576744186</v>
       </c>
       <c r="D11" s="13" t="n">
-        <v>6155.426046511628</v>
+        <v>16860.38208609272</v>
       </c>
       <c r="E11" s="13" t="n">
-        <v>360</v>
+        <v>251</v>
       </c>
       <c r="F11" s="15" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G11" s="13" t="n">
-        <v>138</v>
+        <v>30</v>
       </c>
       <c r="H11" s="15" t="n">
-        <v>772.96</v>
+        <v>2122.76</v>
       </c>
       <c r="I11" s="13" t="n">
-        <v>12.56</v>
+        <v>12.59</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="8" t="inlineStr">
         <is>
-          <t>ENFERMEIRO</t>
+          <t>AUX. DE ADMINISTRACAO</t>
         </is>
       </c>
       <c r="B12" s="9" t="n">
-        <v>14787.75215621105</v>
+        <v>5384.92459141842</v>
       </c>
       <c r="C12" s="10" t="n">
-        <v>13169.33714285714</v>
+        <v>6505.958928571429</v>
       </c>
       <c r="D12" s="9" t="n">
-        <v>16698.0221086262</v>
+        <v>6155.426046511628</v>
       </c>
       <c r="E12" s="9" t="n">
-        <v>252</v>
+        <v>359</v>
       </c>
       <c r="F12" s="11" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="G12" s="9" t="n">
-        <v>31</v>
+        <v>138</v>
       </c>
       <c r="H12" s="11" t="n">
-        <v>1910.27</v>
+        <v>770.5</v>
       </c>
       <c r="I12" s="9" t="n">
-        <v>11.44</v>
+        <v>12.52</v>
       </c>
     </row>
     <row r="13">
@@ -1270,28 +1270,28 @@
         </is>
       </c>
       <c r="B14" s="9" t="n">
-        <v>6503.948242147923</v>
+        <v>6503.189073791348</v>
       </c>
       <c r="C14" s="10" t="n">
-        <v>6924.54</v>
+        <v>6952.685</v>
       </c>
       <c r="D14" s="9" t="n">
-        <v>7089.751495327103</v>
+        <v>7065.996899999999</v>
       </c>
       <c r="E14" s="9" t="n">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="F14" s="11" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="G14" s="9" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H14" s="11" t="n">
-        <v>585.8</v>
+        <v>562.8099999999999</v>
       </c>
       <c r="I14" s="9" t="n">
-        <v>8.26</v>
+        <v>7.97</v>
       </c>
     </row>
     <row r="15">
@@ -1359,29 +1359,29 @@
     <row r="17">
       <c r="A17" s="12" t="inlineStr">
         <is>
-          <t>TEC.DE CONTROLE ADMINISTRATIVO</t>
+          <t>ORIENT. PED.</t>
         </is>
       </c>
       <c r="B17" s="13" t="n">
-        <v>4863.39057404022</v>
+        <v>12074.28337589784</v>
       </c>
       <c r="C17" s="14" t="n">
-        <v>7055.607391304348</v>
+        <v>10885.30727272727</v>
       </c>
       <c r="D17" s="13" t="n">
-        <v>5175.958175944334</v>
+        <v>12849.87514285714</v>
       </c>
       <c r="E17" s="13" t="n">
-        <v>337</v>
+        <v>116</v>
       </c>
       <c r="F17" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G17" s="13" t="n">
         <v>10</v>
       </c>
-      <c r="G17" s="13" t="n">
-        <v>227</v>
-      </c>
       <c r="H17" s="15" t="n">
-        <v>312.57</v>
+        <v>775.59</v>
       </c>
       <c r="I17" s="13" t="n">
         <v>6.04</v>
@@ -1390,94 +1390,94 @@
     <row r="18">
       <c r="A18" s="8" t="inlineStr">
         <is>
-          <t>ORIENT. PED.</t>
+          <t>TEC.DE CONTROLE ADMINISTRATIVO</t>
         </is>
       </c>
       <c r="B18" s="9" t="n">
-        <v>12074.28337589784</v>
+        <v>4866.747340699815</v>
       </c>
       <c r="C18" s="10" t="n">
-        <v>10885.30727272727</v>
+        <v>6582.768482142857</v>
       </c>
       <c r="D18" s="9" t="n">
-        <v>12849.87514285714</v>
+        <v>5175.958175944334</v>
       </c>
       <c r="E18" s="9" t="n">
-        <v>116</v>
+        <v>335</v>
       </c>
       <c r="F18" s="11" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="G18" s="9" t="n">
-        <v>10</v>
+        <v>227</v>
       </c>
       <c r="H18" s="11" t="n">
-        <v>775.59</v>
+        <v>309.21</v>
       </c>
       <c r="I18" s="9" t="n">
-        <v>6.04</v>
+        <v>5.97</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="12" t="inlineStr">
         <is>
-          <t>AGENTE DE COMBATE AS ENDEMIAS</t>
+          <t>TECNICO DE ENFERMAGEM</t>
         </is>
       </c>
       <c r="B19" s="13" t="n">
-        <v>4711.739970845481</v>
+        <v>6934.105323144909</v>
       </c>
       <c r="C19" s="14" t="n">
-        <v>726.47</v>
+        <v>7233.320357142857</v>
       </c>
       <c r="D19" s="13" t="n">
-        <v>4906.384487632509</v>
+        <v>7223.517057553958</v>
       </c>
       <c r="E19" s="13" t="n">
-        <v>37</v>
+        <v>524</v>
       </c>
       <c r="F19" s="15" t="n">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="G19" s="13" t="n">
-        <v>31</v>
+        <v>133</v>
       </c>
       <c r="H19" s="15" t="n">
-        <v>194.64</v>
+        <v>289.41</v>
       </c>
       <c r="I19" s="13" t="n">
-        <v>3.97</v>
+        <v>4.01</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="8" t="inlineStr">
         <is>
-          <t>TECNICO DE ENFERMAGEM</t>
+          <t>AGENTE DE COMBATE AS ENDEMIAS</t>
         </is>
       </c>
       <c r="B20" s="9" t="n">
-        <v>6931.821465786094</v>
+        <v>4711.739970845481</v>
       </c>
       <c r="C20" s="10" t="n">
-        <v>7432.587910447761</v>
+        <v>726.47</v>
       </c>
       <c r="D20" s="9" t="n">
-        <v>7208.516868402534</v>
+        <v>4906.384487632509</v>
       </c>
       <c r="E20" s="9" t="n">
-        <v>526</v>
+        <v>37</v>
       </c>
       <c r="F20" s="11" t="n">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="G20" s="9" t="n">
-        <v>136</v>
+        <v>31</v>
       </c>
       <c r="H20" s="11" t="n">
-        <v>276.7</v>
+        <v>194.64</v>
       </c>
       <c r="I20" s="9" t="n">
-        <v>3.84</v>
+        <v>3.97</v>
       </c>
     </row>
     <row r="21">
@@ -1487,56 +1487,56 @@
         </is>
       </c>
       <c r="B21" s="13" t="n">
-        <v>994.5456962025316</v>
+        <v>995.0665537321333</v>
       </c>
       <c r="C21" s="14" t="n">
-        <v>897.2984615384615</v>
+        <v>921.8030769230769</v>
       </c>
       <c r="D21" s="13" t="n">
-        <v>1028.652635445363</v>
+        <v>1028.074280408542</v>
       </c>
       <c r="E21" s="13" t="n">
-        <v>717</v>
+        <v>714</v>
       </c>
       <c r="F21" s="15" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="G21" s="13" t="n">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="H21" s="15" t="n">
-        <v>34.11</v>
+        <v>33.01</v>
       </c>
       <c r="I21" s="13" t="n">
-        <v>3.32</v>
+        <v>3.21</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="8" t="inlineStr">
         <is>
-          <t>INSPETOR DE ALUNOS</t>
+          <t>CIRURGIAO DENTISTA I 150H</t>
         </is>
       </c>
       <c r="B22" s="9" t="n">
-        <v>4029.07940131579</v>
+        <v>18347.58378571429</v>
       </c>
       <c r="C22" s="10" t="n">
-        <v>3517.005142857143</v>
+        <v>18460.214</v>
       </c>
       <c r="D22" s="9" t="n">
-        <v>4154.60873015873</v>
+        <v>18918.46007633588</v>
       </c>
       <c r="E22" s="9" t="n">
-        <v>159</v>
+        <v>14</v>
       </c>
       <c r="F22" s="11" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G22" s="9" t="n">
-        <v>95</v>
+        <v>13</v>
       </c>
       <c r="H22" s="11" t="n">
-        <v>125.53</v>
+        <v>570.88</v>
       </c>
       <c r="I22" s="9" t="n">
         <v>3.02</v>
@@ -1545,32 +1545,32 @@
     <row r="23">
       <c r="A23" s="12" t="inlineStr">
         <is>
-          <t>CIRURGIAO DENTISTA I 150H</t>
+          <t>INSPETOR DE ALUNOS</t>
         </is>
       </c>
       <c r="B23" s="13" t="n">
-        <v>18355.09246666667</v>
+        <v>4034.850947647449</v>
       </c>
       <c r="C23" s="14" t="n">
-        <v>0</v>
+        <v>3450.125869565218</v>
       </c>
       <c r="D23" s="13" t="n">
-        <v>18918.46007633588</v>
+        <v>4154.60873015873</v>
       </c>
       <c r="E23" s="13" t="n">
-        <v>15</v>
+        <v>158</v>
       </c>
       <c r="F23" s="15" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G23" s="13" t="n">
-        <v>13</v>
+        <v>95</v>
       </c>
       <c r="H23" s="15" t="n">
-        <v>563.37</v>
+        <v>119.76</v>
       </c>
       <c r="I23" s="13" t="n">
-        <v>2.98</v>
+        <v>2.88</v>
       </c>
     </row>
     <row r="24">
@@ -1583,25 +1583,25 @@
         <v>14609.11808243728</v>
       </c>
       <c r="C24" s="10" t="n">
-        <v>14468.67727272727</v>
+        <v>14666.65153846154</v>
       </c>
       <c r="D24" s="9" t="n">
-        <v>15033.96659021407</v>
+        <v>15031.75326687117</v>
       </c>
       <c r="E24" s="9" t="n">
         <v>90</v>
       </c>
       <c r="F24" s="11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G24" s="9" t="n">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="H24" s="11" t="n">
-        <v>424.85</v>
+        <v>422.64</v>
       </c>
       <c r="I24" s="9" t="n">
-        <v>2.83</v>
+        <v>2.81</v>
       </c>
     </row>
     <row r="25">
@@ -1731,94 +1731,94 @@
     <row r="29">
       <c r="A29" s="12" t="inlineStr">
         <is>
-          <t>CHEFE DE SECAO</t>
+          <t>ASSISTENTE DE SECRETARIA E EXPEDIENTE (FG)</t>
         </is>
       </c>
       <c r="B29" s="13" t="n">
-        <v>11384.01562782805</v>
+        <v>10434.68347826087</v>
       </c>
       <c r="C29" s="14" t="n">
-        <v>8733.377142857144</v>
+        <v>17069.95666666667</v>
       </c>
       <c r="D29" s="13" t="n">
-        <v>11402.04585161964</v>
+        <v>10481.98141666667</v>
       </c>
       <c r="E29" s="13" t="n">
-        <v>198</v>
+        <v>60</v>
       </c>
       <c r="F29" s="15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G29" s="13" t="n">
-        <v>111</v>
+        <v>23</v>
       </c>
       <c r="H29" s="15" t="n">
-        <v>18.03</v>
+        <v>47.3</v>
       </c>
       <c r="I29" s="13" t="n">
-        <v>0.16</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="8" t="inlineStr">
         <is>
-          <t>PEBII ED.FISICA</t>
+          <t>CHEFE DE SECAO</t>
         </is>
       </c>
       <c r="B30" s="9" t="n">
-        <v>11021.70415730337</v>
+        <v>11396.28158314351</v>
       </c>
       <c r="C30" s="10" t="n">
-        <v>13201.338125</v>
+        <v>9645.055862068966</v>
       </c>
       <c r="D30" s="9" t="n">
-        <v>11010.9685882353</v>
+        <v>11413.15107708553</v>
       </c>
       <c r="E30" s="9" t="n">
-        <v>50</v>
+        <v>197</v>
       </c>
       <c r="F30" s="11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G30" s="9" t="n">
-        <v>41</v>
+        <v>110</v>
       </c>
       <c r="H30" s="11" t="n">
-        <v>-10.74</v>
+        <v>16.87</v>
       </c>
       <c r="I30" s="9" t="n">
-        <v>-0.1</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="12" t="inlineStr">
         <is>
-          <t>ASSISTENTE DE SECRETARIA E EXPEDIENTE (FG)</t>
+          <t>PEBII ED.FISICA</t>
         </is>
       </c>
       <c r="B31" s="13" t="n">
-        <v>10529.4730952381</v>
+        <v>11021.70415730337</v>
       </c>
       <c r="C31" s="14" t="n">
-        <v>0</v>
+        <v>13201.338125</v>
       </c>
       <c r="D31" s="13" t="n">
-        <v>10481.98141666667</v>
+        <v>11010.9685882353</v>
       </c>
       <c r="E31" s="13" t="n">
-        <v>61</v>
+        <v>50</v>
       </c>
       <c r="F31" s="15" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G31" s="13" t="n">
-        <v>23</v>
+        <v>41</v>
       </c>
       <c r="H31" s="15" t="n">
-        <v>-47.49</v>
+        <v>-10.74</v>
       </c>
       <c r="I31" s="13" t="n">
-        <v>-0.45</v>
+        <v>-0.1</v>
       </c>
     </row>
     <row r="32">
@@ -1890,28 +1890,28 @@
         </is>
       </c>
       <c r="B34" s="9" t="n">
-        <v>4420.368410067155</v>
+        <v>4421.413244593359</v>
       </c>
       <c r="C34" s="10" t="n">
-        <v>4275.333803418804</v>
+        <v>4327.896479999999</v>
       </c>
       <c r="D34" s="9" t="n">
-        <v>4345.757714723926</v>
+        <v>4331.328136256852</v>
       </c>
       <c r="E34" s="9" t="n">
-        <v>1609</v>
+        <v>1598</v>
       </c>
       <c r="F34" s="11" t="n">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="G34" s="9" t="n">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="H34" s="11" t="n">
-        <v>-74.61</v>
+        <v>-90.09</v>
       </c>
       <c r="I34" s="9" t="n">
-        <v>-1.72</v>
+        <v>-2.08</v>
       </c>
     </row>
     <row r="35">
@@ -2014,28 +2014,28 @@
         </is>
       </c>
       <c r="B38" s="9" t="n">
-        <v>11326.35278264024</v>
+        <v>11325.93709283796</v>
       </c>
       <c r="C38" s="10" t="n">
-        <v>10573.1725087108</v>
+        <v>10745.36656565657</v>
       </c>
       <c r="D38" s="9" t="n">
-        <v>10768.17515451174</v>
+        <v>10782.53539340102</v>
       </c>
       <c r="E38" s="9" t="n">
-        <v>2171</v>
+        <v>2163</v>
       </c>
       <c r="F38" s="11" t="n">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="G38" s="9" t="n">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="H38" s="11" t="n">
-        <v>-558.1799999999999</v>
+        <v>-543.4</v>
       </c>
       <c r="I38" s="9" t="n">
-        <v>-5.18</v>
+        <v>-5.04</v>
       </c>
     </row>
     <row r="39">
@@ -2045,28 +2045,28 @@
         </is>
       </c>
       <c r="B39" s="13" t="n">
-        <v>5433.158392857143</v>
+        <v>5417.746440677965</v>
       </c>
       <c r="C39" s="14" t="n">
-        <v>8251.130000000001</v>
+        <v>7527.875416666667</v>
       </c>
       <c r="D39" s="13" t="n">
         <v>5049.654104477612</v>
       </c>
       <c r="E39" s="13" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F39" s="15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G39" s="13" t="n">
         <v>69</v>
       </c>
       <c r="H39" s="15" t="n">
-        <v>-383.5</v>
+        <v>-368.09</v>
       </c>
       <c r="I39" s="13" t="n">
-        <v>-7.59</v>
+        <v>-7.29</v>
       </c>
     </row>
     <row r="40">
@@ -2138,63 +2138,32 @@
         </is>
       </c>
       <c r="B42" s="9" t="n">
-        <v>1813.164491856169</v>
+        <v>1812.38808530657</v>
       </c>
       <c r="C42" s="10" t="n">
-        <v>1854.588681318681</v>
+        <v>1899.488295819936</v>
       </c>
       <c r="D42" s="9" t="n">
-        <v>1493.283056443025</v>
+        <v>1472.960546875</v>
       </c>
       <c r="E42" s="9" t="n">
-        <v>3627</v>
+        <v>3612</v>
       </c>
       <c r="F42" s="11" t="n">
-        <v>35</v>
+        <v>59</v>
       </c>
       <c r="G42" s="9" t="n">
-        <v>210</v>
+        <v>201</v>
       </c>
       <c r="H42" s="11" t="n">
-        <v>-319.88</v>
+        <v>-339.43</v>
       </c>
       <c r="I42" s="9" t="n">
-        <v>-21.42</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="12" t="inlineStr">
-        <is>
-          <t>SUPERV. ENS.</t>
-        </is>
-      </c>
-      <c r="B43" s="13" t="n">
-        <v>24359.10083969466</v>
-      </c>
-      <c r="C43" s="14" t="n">
-        <v>15878.47</v>
-      </c>
-      <c r="D43" s="13" t="n">
-        <v>17490.49276190476</v>
-      </c>
-      <c r="E43" s="13" t="n">
-        <v>12</v>
-      </c>
-      <c r="F43" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="G43" s="13" t="n">
-        <v>10</v>
-      </c>
-      <c r="H43" s="15" t="n">
-        <v>-6868.61</v>
-      </c>
-      <c r="I43" s="13" t="n">
-        <v>-39.27</v>
+        <v>-23.04</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I43"/>
+  <autoFilter ref="A1:I42"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>